--- a/DataTables/DetailText/剧情/023_02治疗成功.xlsx
+++ b/DataTables/DetailText/剧情/023_02治疗成功.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{689868DB-74B9-4646-8E9C-EC0CE3128570}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F939A524-D6AC-413B-8A72-FC4FE0EBD408}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="59">
   <si>
     <t>StoryID</t>
   </si>
@@ -61,10 +61,6 @@
   </si>
   <si>
     <t>PortraitSide</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>left</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -140,6 +136,9 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
+    <t>current_scene</t>
+  </si>
+  <si>
     <t>story_npc_cured</t>
   </si>
   <si>
@@ -155,40 +154,13 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>半夏</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>res://Assets/Background/023/023.png</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>呜呜呜，夫人到底是得了什么病啊。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>李东璧</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>芷兰…我们有孩子了…</t>
-    <rPh sb="0" eb="1">
-      <t>シ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ワ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>吴芷兰</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>真的吗！哎呀，太好了，是男孩儿女孩儿？</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
+    <r>
+      <t>姑娘</t>
+    </r>
     <r>
       <rPr>
         <sz val="11"/>
@@ -197,7 +169,7 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>现</t>
+      <t>这</t>
     </r>
     <r>
       <rPr>
@@ -207,7 +179,63 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>在</t>
+      <t>病是肺气虚，平日注意避风避寒，开副</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>补肺汤调养调养。早上练练六字诀中的呬字决，舒畅胸中气机。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>谢飞燕</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>…</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>姑娘可是有什么心事？</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>left</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>金姨妈</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>王百堂</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>hide</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>半夏</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>mid</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>成天好吃好喝的伺候着，她能有什么心事。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>先生，</t>
     </r>
     <r>
       <rPr>
@@ -217,7 +245,7 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>还</t>
+      <t>刚</t>
     </r>
     <r>
       <rPr>
@@ -227,7 +255,25 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>看不出来，男孩儿女孩儿都一</t>
+      <t>才那姑娘是得了什么病啊？</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>您是？</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>哦，那姑娘所患的是肺气虚，并无大碍，只是看起来似乎有心事。您可知其中原委？</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>哎哟？这里面有事儿，快说来听听。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>小生是姑娘的一位相</t>
     </r>
     <r>
       <rPr>
@@ -237,7 +283,7 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>样</t>
+      <t>识</t>
     </r>
     <r>
       <rPr>
@@ -247,7 +293,7 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>，我</t>
+      <t>，担心姑娘身体，来</t>
     </r>
     <r>
       <rPr>
@@ -257,7 +303,7 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>们</t>
+      <t>问问</t>
     </r>
     <r>
       <rPr>
@@ -267,14 +313,11 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>要当爹当娘了。</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>哇，恭喜恭喜，真是菩萨保佑，我去把</t>
-    </r>
+      <t>大夫。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -283,7 +326,7 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>这</t>
+      <t>实</t>
     </r>
     <r>
       <rPr>
@@ -293,7 +336,7 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>喜事告</t>
+      <t>不相</t>
     </r>
     <r>
       <rPr>
@@ -303,7 +346,7 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>诉</t>
+      <t>瞒</t>
     </r>
     <r>
       <rPr>
@@ -313,7 +356,31 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>老</t>
+      <t>，小生在柳月坊与</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>飞燕相识，一见倾心，私底下定了终身。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>sick</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>…多谢先生。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>那就多</t>
     </r>
     <r>
       <rPr>
@@ -323,7 +390,7 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>爷</t>
+      <t>谢</t>
     </r>
     <r>
       <rPr>
@@ -333,8 +400,142 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>去！</t>
-    </r>
+      <t>大夫了，走吧女儿。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>原想着凑够五百两白</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>银</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>给</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>她</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>赎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>身。可她那</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>老鸨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>坐地起价一千两，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这让我们上哪去凑这么多银子啊…</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>想必姑娘是因</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>为这</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>事急坏了身子。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>唉，又是一对儿苦命的鸳鸯。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>陈皮</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>你在这儿干啥呢，夫人找你呢。</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -519,7 +720,7 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -827,49 +1028,49 @@
         <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="D1" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="K1" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="N1" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="P1" s="16" t="s">
         <v>18</v>
-      </c>
-      <c r="F1" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="G1" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="H1" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="I1" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="K1" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="L1" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M1" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="N1" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="O1" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="P1" s="16" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.4">
@@ -883,10 +1084,10 @@
         <v>29</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
@@ -976,7 +1177,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
@@ -1007,10 +1208,10 @@
         <v>4</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H1" s="6" t="s">
         <v>5</v>
@@ -1027,15 +1228,15 @@
         <v>33</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="8"/>
       <c r="G2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
@@ -1046,16 +1247,18 @@
         <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="2"/>
+        <v>35</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>51</v>
+      </c>
       <c r="F3" s="8"/>
       <c r="G3" s="2"/>
       <c r="H3" s="1" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
@@ -1066,16 +1269,16 @@
         <v>6</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>9</v>
+        <v>33</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="8"/>
       <c r="G4" s="2"/>
       <c r="H4" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
@@ -1086,16 +1289,16 @@
         <v>6</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
-      <c r="H5" s="19" t="s">
-        <v>40</v>
+      <c r="H5" s="1" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
@@ -1106,77 +1309,255 @@
         <v>6</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
+      <c r="F6" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="G6" s="2"/>
       <c r="H6" s="1" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
+      <c r="B7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
+      <c r="H7" s="1" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="2"/>
+      <c r="B8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
+      <c r="G8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="2"/>
+      <c r="B9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
+      <c r="H9" s="3" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="2"/>
+      <c r="B10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
+      <c r="H10" s="3" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>10</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="2"/>
+      <c r="B11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
+      <c r="H11" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="19" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>

--- a/DataTables/DetailText/剧情/023_02治疗成功.xlsx
+++ b/DataTables/DetailText/剧情/023_02治疗成功.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F939A524-D6AC-413B-8A72-FC4FE0EBD408}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB702BA9-740F-4C71-9FDE-0AD5BA847379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="60">
   <si>
     <t>StoryID</t>
   </si>
@@ -531,11 +531,27 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>陈皮</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>你在这儿干啥呢，夫人找你呢。</t>
+    <t>吴芷兰</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>相公我们想办法帮帮他们吧。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>我也想</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>帮他们，可怎么帮呢？</t>
+    </r>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -669,7 +685,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -720,6 +736,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1177,7 +1196,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
@@ -1536,28 +1555,108 @@
       <c r="B17" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="20" t="s">
         <v>57</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
-      <c r="H17" s="3" t="s">
+      <c r="H17" s="20" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="2"/>
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
+      <c r="H18" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A25" s="1"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>

--- a/DataTables/DetailText/剧情/023_02治疗成功.xlsx
+++ b/DataTables/DetailText/剧情/023_02治疗成功.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB702BA9-740F-4C71-9FDE-0AD5BA847379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A2280A0-D119-4F90-BCF4-DBFF58ED67D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -158,8 +158,48 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <r>
-      <t>姑娘</t>
+    <t>谢飞燕</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>…</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>姑娘可是有什么心事？</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>left</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>金姨妈</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>王百堂</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>hide</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>半夏</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>mid</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>成天好吃好喝的伺候着，她能有什么心事。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>先生，</t>
     </r>
     <r>
       <rPr>
@@ -169,7 +209,7 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>这</t>
+      <t>刚</t>
     </r>
     <r>
       <rPr>
@@ -179,7 +219,108 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>病是肺气虚，平日注意避风避寒，开副</t>
+      <t>才那姑娘是得了什么病啊？</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>您是？</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>哦，那姑娘所患的是肺气虚，并无大碍，只是看起来似乎有心事。您可知其中原委？</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>哎哟？这里面有事儿，快说来听听。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>小生是姑娘的一位相</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>识</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>，担心姑娘身体，来</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>问问</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>大夫。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>实</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>不相</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>瞒</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>，小生在柳月坊与</t>
     </r>
     <r>
       <rPr>
@@ -189,53 +330,21 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>补肺汤调养调养。早上练练六字诀中的呬字决，舒畅胸中气机。</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>谢飞燕</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>…</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>姑娘可是有什么心事？</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>left</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>金姨妈</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>王百堂</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>hide</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>半夏</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>mid</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>成天好吃好喝的伺候着，她能有什么心事。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>先生，</t>
+      <t>飞燕相识，一见倾心，私底下定了终身。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>sick</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>…多谢先生。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>那就多</t>
     </r>
     <r>
       <rPr>
@@ -245,7 +354,7 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>刚</t>
+      <t>谢</t>
     </r>
     <r>
       <rPr>
@@ -255,25 +364,13 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>才那姑娘是得了什么病啊？</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>您是？</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>哦，那姑娘所患的是肺气虚，并无大碍，只是看起来似乎有心事。您可知其中原委？</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>哎哟？这里面有事儿，快说来听听。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>小生是姑娘的一位相</t>
+      <t>大夫了，走吧女儿。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>原想着凑够五百两白</t>
     </r>
     <r>
       <rPr>
@@ -283,7 +380,7 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>识</t>
+      <t>银</t>
     </r>
     <r>
       <rPr>
@@ -293,7 +390,7 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>，担心姑娘身体，来</t>
+      <t>，</t>
     </r>
     <r>
       <rPr>
@@ -303,7 +400,7 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>问问</t>
+      <t>给</t>
     </r>
     <r>
       <rPr>
@@ -313,11 +410,8 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>大夫。</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
+      <t>她</t>
+    </r>
     <r>
       <rPr>
         <sz val="11"/>
@@ -326,7 +420,7 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>实</t>
+      <t>赎</t>
     </r>
     <r>
       <rPr>
@@ -336,7 +430,43 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>不相</t>
+      <t>身。可她那</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>老鸨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>坐地起价一千两，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这让我们上哪去凑这么多银子啊…</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>想必姑娘是因</t>
     </r>
     <r>
       <rPr>
@@ -346,7 +476,7 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>瞒</t>
+      <t>为这</t>
     </r>
     <r>
       <rPr>
@@ -356,7 +486,21 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>，小生在柳月坊与</t>
+      <t>事急坏了身子。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>唉，又是一对儿苦命的鸳鸯。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>吴芷兰</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>我也想</t>
     </r>
     <r>
       <rPr>
@@ -366,21 +510,13 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>飞燕相识，一见倾心，私底下定了终身。</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>sick</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>…多谢先生。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>那就多</t>
+      <t>帮他们，可怎么帮呢？</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>姑娘</t>
     </r>
     <r>
       <rPr>
@@ -390,7 +526,7 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>谢</t>
+      <t>这</t>
     </r>
     <r>
       <rPr>
@@ -400,73 +536,7 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>大夫了，走吧女儿。</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>原想着凑够五百两白</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>银</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>给</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>她</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>赎</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>身。可她那</t>
+      <t>病是肺气虚，平日注意避风避寒，开副</t>
     </r>
     <r>
       <rPr>
@@ -476,82 +546,12 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>老鸨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>坐地起价一千两，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>这让我们上哪去凑这么多银子啊…</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>想必姑娘是因</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>为这</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>事急坏了身子。</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>唉，又是一对儿苦命的鸳鸯。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>吴芷兰</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>相公我们想办法帮帮他们吧。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>我也想</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>帮他们，可怎么帮呢？</t>
-    </r>
+      <t>补肺汤调养调养。早上练练六字诀中的呬字诀，舒畅胸中气机。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>相公咱想办法帮帮他们吧。</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1255,7 +1255,7 @@
         <v>28</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
@@ -1266,18 +1266,18 @@
         <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F3" s="8"/>
       <c r="G3" s="2"/>
       <c r="H3" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
@@ -1297,7 +1297,7 @@
       <c r="F4" s="8"/>
       <c r="G4" s="2"/>
       <c r="H4" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
@@ -1308,16 +1308,16 @@
         <v>6</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
@@ -1328,18 +1328,18 @@
         <v>6</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
@@ -1350,20 +1350,20 @@
         <v>6</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>10</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
@@ -1374,10 +1374,10 @@
         <v>6</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
@@ -1385,7 +1385,7 @@
         <v>28</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
@@ -1405,7 +1405,7 @@
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
@@ -1416,16 +1416,16 @@
         <v>6</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
@@ -1445,7 +1445,7 @@
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
@@ -1456,16 +1456,16 @@
         <v>6</v>
       </c>
       <c r="C12" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>43</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
@@ -1476,16 +1476,16 @@
         <v>6</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="19" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
@@ -1496,16 +1496,16 @@
         <v>6</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
@@ -1525,7 +1525,7 @@
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
@@ -1536,16 +1536,16 @@
         <v>6</v>
       </c>
       <c r="C16" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>43</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
@@ -1556,16 +1556,16 @@
         <v>6</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
@@ -1585,7 +1585,7 @@
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">

--- a/DataTables/DetailText/剧情/023_02治疗成功.xlsx
+++ b/DataTables/DetailText/剧情/023_02治疗成功.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A2280A0-D119-4F90-BCF4-DBFF58ED67D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2D7F590-D8B6-4D97-8796-908587D852D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="2205" windowWidth="21600" windowHeight="11423" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,26 +21,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="60">
-  <si>
-    <t>StoryID</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="64">
   <si>
     <t>LineIndex</t>
   </si>
@@ -80,66 +66,16 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>StoryName</t>
-  </si>
-  <si>
-    <t>TriggerType</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>TriggerScene</t>
-  </si>
-  <si>
-    <t>NpcID</t>
-  </si>
-  <si>
     <t>PlayOnce</t>
   </si>
   <si>
-    <t>ReturnScene</t>
-  </si>
-  <si>
     <t>SortIndex</t>
   </si>
   <si>
     <t>clinic</t>
   </si>
   <si>
-    <t>ClinicNpcPortraitPath</t>
-  </si>
-  <si>
-    <t>TriggerStoryID</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>TriggerDay</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Reputation</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Experience</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>TriggerReputation</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>TriggerEntryId</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Disease</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>current_scene</t>
-  </si>
-  <si>
-    <t>story_npc_cured</t>
   </si>
   <si>
     <t>023_02</t>
@@ -553,17 +489,105 @@
   <si>
     <t>相公咱想办法帮帮他们吧。</t>
     <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>剧情ID</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>剧情名</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>触发场景</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>触发天数</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <r>
+      <t>金</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>钱判定</t>
+    </r>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>触发金钱</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>名望判定</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>触发名望</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>触发条目</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>触发剧情ID</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>触发治疗结果</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>播放后</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>人物ID</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>疾病</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>人物立绘路径</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>奖励金钱</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>奖励名望</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>奖励心得</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>cured</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -577,7 +601,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -598,20 +622,12 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Noto Sans JP"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Noto Sans JP"/>
@@ -625,8 +641,30 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Noto Sans JP"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -641,20 +679,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FF92D050"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFFF0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF200"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -685,7 +725,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -711,24 +751,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -741,9 +770,40 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1021,175 +1081,204 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
-  <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:T20"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="24.875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.46484375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="7" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.9296875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.06640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.1328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.06640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="6" t="s">
+    <row r="1" spans="1:20" s="23" customFormat="1">
+      <c r="A1" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="E1" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="F1" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="I1" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="K1" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="L1" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="M1" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="N1" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="O1" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="P1" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q1" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="R1" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="S1" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="T1" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="6" t="s">
+    </row>
+    <row r="2" spans="1:20" s="23" customFormat="1">
+      <c r="A2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="6" t="s">
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="F1" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="G1" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="H1" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="I1" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="J1" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="K1" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="M1" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="N1" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="O1" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="P1" s="16" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A2" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="1" t="b">
+      <c r="K2" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="L2" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="24"/>
+      <c r="N2" s="25"/>
+      <c r="O2" s="25"/>
+      <c r="P2" s="25"/>
+      <c r="Q2" s="25"/>
+      <c r="R2" s="26"/>
+      <c r="S2" s="26" t="b">
         <v>1</v>
       </c>
-      <c r="P2" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="C3" s="10"/>
-      <c r="H3" s="14"/>
-      <c r="L3" s="18"/>
-      <c r="O3" s="11"/>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="C4" s="10"/>
-      <c r="H4" s="14"/>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="C5" s="10"/>
-      <c r="H5" s="14"/>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="C6" s="10"/>
-      <c r="H6" s="14"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="C7" s="10"/>
-      <c r="H7" s="14"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="C8" s="10"/>
-      <c r="H8" s="14"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H9" s="14"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H10" s="14"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H11" s="14"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H12" s="14"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H13" s="14"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H14" s="14"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H15" s="14"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H16" s="14"/>
-    </row>
-    <row r="17" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H17" s="14"/>
-    </row>
-    <row r="18" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H18" s="14"/>
-    </row>
-    <row r="19" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H19" s="14"/>
-    </row>
-    <row r="20" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H20" s="14"/>
+      <c r="T2" s="26"/>
+    </row>
+    <row r="3" spans="1:20">
+      <c r="C3" s="9"/>
+      <c r="H3" s="11"/>
+      <c r="L3" s="13"/>
+      <c r="O3" s="10"/>
+    </row>
+    <row r="4" spans="1:20">
+      <c r="C4" s="9"/>
+      <c r="H4" s="11"/>
+    </row>
+    <row r="5" spans="1:20">
+      <c r="C5" s="9"/>
+      <c r="H5" s="11"/>
+    </row>
+    <row r="6" spans="1:20">
+      <c r="C6" s="9"/>
+      <c r="H6" s="11"/>
+    </row>
+    <row r="7" spans="1:20">
+      <c r="C7" s="9"/>
+      <c r="H7" s="11"/>
+    </row>
+    <row r="8" spans="1:20">
+      <c r="C8" s="9"/>
+      <c r="H8" s="11"/>
+    </row>
+    <row r="9" spans="1:20">
+      <c r="H9" s="11"/>
+    </row>
+    <row r="10" spans="1:20">
+      <c r="H10" s="11"/>
+    </row>
+    <row r="11" spans="1:20">
+      <c r="H11" s="11"/>
+    </row>
+    <row r="12" spans="1:20">
+      <c r="H12" s="11"/>
+    </row>
+    <row r="13" spans="1:20">
+      <c r="H13" s="11"/>
+    </row>
+    <row r="14" spans="1:20">
+      <c r="H14" s="11"/>
+    </row>
+    <row r="15" spans="1:20">
+      <c r="H15" s="11"/>
+    </row>
+    <row r="16" spans="1:20">
+      <c r="H16" s="11"/>
+    </row>
+    <row r="17" spans="8:8">
+      <c r="H17" s="11"/>
+    </row>
+    <row r="18" spans="8:8">
+      <c r="H18" s="11"/>
+    </row>
+    <row r="19" spans="8:8">
+      <c r="H19" s="11"/>
+    </row>
+    <row r="20" spans="8:8">
+      <c r="H20" s="11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
+  <dataValidations count="5">
+    <dataValidation type="list" sqref="C2" xr:uid="{58970059-8D50-4A9B-B6AD-1DA2264E44E9}">
+      <formula1>"clinic,night,night_end"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="E2 G2" xr:uid="{A31730C7-D056-4402-B229-43BCCC77E431}">
+      <formula1>"≥,≤"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="L2" xr:uid="{5CE4A361-66B0-400C-818F-22025AE9F423}">
+      <formula1>"clinic,night,end_game"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="S2" xr:uid="{E4337D0E-7E9B-4ED8-974F-B981AA711184}">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="K2" xr:uid="{CA429BE4-EA89-41B7-8C04-96270953739B}">
+      <formula1>"cured,failed"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1197,398 +1286,398 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
   <dimension ref="A1:H25"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8">
       <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="D1" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:8" ht="33">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="8"/>
       <c r="G2" s="2" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="F3" s="8"/>
       <c r="G3" s="2"/>
       <c r="H3" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="8"/>
       <c r="G4" s="2"/>
       <c r="H4" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="2" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="1">
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="1">
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" s="1">
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" s="1">
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
-      <c r="H13" s="19" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H13" s="14" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" s="1">
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" s="1">
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" s="1">
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" s="1">
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C17" s="20" t="s">
-        <v>56</v>
+        <v>5</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>41</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
-      <c r="H17" s="20" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H17" s="15" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" s="1">
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="3"/>
@@ -1598,7 +1687,7 @@
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="3"/>
@@ -1608,7 +1697,7 @@
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="3"/>
@@ -1618,7 +1707,7 @@
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="3"/>
@@ -1628,7 +1717,7 @@
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="3"/>
@@ -1638,7 +1727,7 @@
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="3"/>
@@ -1648,7 +1737,7 @@
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="3"/>

--- a/DataTables/DetailText/剧情/023_02治疗成功.xlsx
+++ b/DataTables/DetailText/剧情/023_02治疗成功.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2D7F590-D8B6-4D97-8796-908587D852D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECED9F32-B736-44CF-B916-D5EEBE4CD829}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2205" windowWidth="21600" windowHeight="11423" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19365" yWindow="4455" windowWidth="16035" windowHeight="8025" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,12 +21,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="65">
   <si>
     <t>LineIndex</t>
   </si>
@@ -577,6 +588,10 @@
   </si>
   <si>
     <t>cured</t>
+  </si>
+  <si>
+    <t>Music</t>
+    <phoneticPr fontId="9"/>
   </si>
 </sst>
 </file>
@@ -587,7 +602,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -601,7 +616,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -622,7 +637,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -725,7 +740,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -801,9 +816,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1082,25 +1100,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:T20"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="7.46484375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="7" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.9296875" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.06640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="7" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.1328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.06640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.19921875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="23" customFormat="1">
+    <row r="1" spans="1:20" s="23" customFormat="1" ht="18">
       <c r="A1" s="16" t="s">
         <v>45</v>
       </c>
@@ -1162,7 +1180,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="23" customFormat="1">
+    <row r="2" spans="1:20" s="23" customFormat="1" ht="18">
       <c r="A2" s="5" t="s">
         <v>15</v>
       </c>
@@ -1285,21 +1303,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1324,8 +1342,11 @@
       <c r="H1" s="6" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" ht="33">
+      <c r="I1" s="27" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1346,8 +1367,9 @@
       <c r="H2" s="1" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1368,8 +1390,9 @@
       <c r="H3" s="1" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1388,8 +1411,9 @@
       <c r="H4" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="I4" s="1"/>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1408,8 +1432,9 @@
       <c r="H5" s="1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1430,8 +1455,9 @@
       <c r="H6" s="1" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1454,8 +1480,9 @@
       <c r="H7" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="I7" s="1"/>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1476,8 +1503,9 @@
       <c r="H8" s="3" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="I8" s="1"/>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1496,8 +1524,9 @@
       <c r="H9" s="3" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="I9" s="1"/>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1516,8 +1545,9 @@
       <c r="H10" s="3" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="I10" s="1"/>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -1536,8 +1566,9 @@
       <c r="H11" s="3" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="12" spans="1:8">
+      <c r="I11" s="1"/>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -1556,8 +1587,9 @@
       <c r="H12" s="3" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="13" spans="1:8">
+      <c r="I12" s="1"/>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -1576,8 +1608,9 @@
       <c r="H13" s="14" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="14" spans="1:8">
+      <c r="I13" s="1"/>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -1596,8 +1629,9 @@
       <c r="H14" s="3" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="15" spans="1:8">
+      <c r="I14" s="1"/>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -1616,8 +1650,9 @@
       <c r="H15" s="3" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="16" spans="1:8">
+      <c r="I15" s="1"/>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -1636,8 +1671,9 @@
       <c r="H16" s="3" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="17" spans="1:8">
+      <c r="I16" s="1"/>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -1656,8 +1692,9 @@
       <c r="H17" s="15" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="18" spans="1:8">
+      <c r="I17" s="1"/>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -1676,8 +1713,9 @@
       <c r="H18" s="3" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="19" spans="1:8">
+      <c r="I18" s="1"/>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="3"/>
@@ -1686,8 +1724,9 @@
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
-    </row>
-    <row r="20" spans="1:8">
+      <c r="I19" s="1"/>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="3"/>
@@ -1696,8 +1735,9 @@
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
-    </row>
-    <row r="21" spans="1:8">
+      <c r="I20" s="1"/>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="3"/>
@@ -1706,8 +1746,9 @@
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
-    </row>
-    <row r="22" spans="1:8">
+      <c r="I21" s="1"/>
+    </row>
+    <row r="22" spans="1:9">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="3"/>
@@ -1716,8 +1757,9 @@
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
-    </row>
-    <row r="23" spans="1:8">
+      <c r="I22" s="1"/>
+    </row>
+    <row r="23" spans="1:9">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="3"/>
@@ -1726,8 +1768,9 @@
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
-    </row>
-    <row r="24" spans="1:8">
+      <c r="I23" s="1"/>
+    </row>
+    <row r="24" spans="1:9">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="3"/>
@@ -1736,8 +1779,9 @@
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
-    </row>
-    <row r="25" spans="1:8">
+      <c r="I24" s="1"/>
+    </row>
+    <row r="25" spans="1:9">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="3"/>
@@ -1746,6 +1790,7 @@
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
+      <c r="I25" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>

--- a/DataTables/DetailText/剧情/023_02治疗成功.xlsx
+++ b/DataTables/DetailText/剧情/023_02治疗成功.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECED9F32-B736-44CF-B916-D5EEBE4CD829}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51238C80-81F5-4606-B358-1105F5C0980F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19365" yWindow="4455" windowWidth="16035" windowHeight="8025" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -317,102 +317,6 @@
   </si>
   <si>
     <r>
-      <t>原想着凑够五百两白</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>银</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>给</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>她</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>赎</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>身。可她那</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>老鸨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>坐地起价一千两，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>这让我们上哪去凑这么多银子啊…</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
       <t>想必姑娘是因</t>
     </r>
     <r>
@@ -592,6 +496,122 @@
   <si>
     <t>Music</t>
     <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <r>
+      <t>原想着凑够五百两</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>银子</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>给</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>她</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>赎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>身。可那</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>老鸨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>坐地起价，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>张口就要</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>一千两，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这让我们上哪去凑这么多银子啊…</t>
+    </r>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -1120,58 +1140,58 @@
   <sheetData>
     <row r="1" spans="1:20" s="23" customFormat="1" ht="18">
       <c r="A1" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="C1" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="D1" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="E1" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="F1" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="G1" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="H1" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="H1" s="19" t="s">
+      <c r="I1" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="I1" s="19" t="s">
+      <c r="J1" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="19" t="s">
+      <c r="K1" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="K1" s="19" t="s">
+      <c r="L1" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="L1" s="20" t="s">
+      <c r="M1" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="M1" s="21" t="s">
+      <c r="N1" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="N1" s="21" t="s">
+      <c r="O1" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="O1" s="21" t="s">
+      <c r="P1" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="P1" s="21" t="s">
+      <c r="Q1" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="Q1" s="21" t="s">
+      <c r="R1" s="21" t="s">
         <v>61</v>
-      </c>
-      <c r="R1" s="21" t="s">
-        <v>62</v>
       </c>
       <c r="S1" s="22" t="s">
         <v>11</v>
@@ -1200,7 +1220,7 @@
         <v>17</v>
       </c>
       <c r="K2" s="25" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="L2" s="25" t="s">
         <v>13</v>
@@ -1343,7 +1363,7 @@
         <v>4</v>
       </c>
       <c r="I1" s="27" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1365,7 +1385,7 @@
         <v>14</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I2" s="1"/>
     </row>
@@ -1627,7 +1647,7 @@
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="I14" s="1"/>
     </row>
@@ -1648,7 +1668,7 @@
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I15" s="1"/>
     </row>
@@ -1669,7 +1689,7 @@
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I16" s="1"/>
     </row>
@@ -1681,7 +1701,7 @@
         <v>5</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>22</v>
@@ -1690,7 +1710,7 @@
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I17" s="1"/>
     </row>
@@ -1711,7 +1731,7 @@
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I18" s="1"/>
     </row>
